--- a/testcases/Test_Data/testCase_data.XLSX
+++ b/testcases/Test_Data/testCase_data.XLSX
@@ -502,7 +502,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="F2" s="1">
